--- a/data/trans_orig/IQ23_R2-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ23_R2-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2960</t>
+          <t>3213</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10688</t>
+          <t>11032</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2743</t>
+          <t>3159</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10520</t>
+          <t>11306</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7607</t>
+          <t>7535</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18053</t>
+          <t>17871</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,92%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35509</t>
+          <t>35375</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>51966</t>
+          <t>51743</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>48,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>45542</t>
+          <t>45014</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>62892</t>
+          <t>61900</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,44%</t>
+          <t>51,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>86201</t>
+          <t>86145</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>109214</t>
+          <t>110027</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>48,76%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>47697</t>
+          <t>47752</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>64003</t>
+          <t>64163</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>45,17%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>60,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>51317</t>
+          <t>51936</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>68318</t>
+          <t>68118</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>42,79%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>103306</t>
+          <t>102722</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>127097</t>
+          <t>127054</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>56,3%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1756</t>
+          <t>1696</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8156</t>
+          <t>7718</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1256</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7767</t>
+          <t>7186</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3951</t>
+          <t>4004</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>12499</t>
+          <t>12570</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>47373</t>
+          <t>47306</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>68711</t>
+          <t>68895</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>41406</t>
+          <t>41390</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>62645</t>
+          <t>62145</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>93455</t>
+          <t>93644</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>123149</t>
+          <t>124205</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,6%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>178644</t>
+          <t>178694</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>200962</t>
+          <t>201019</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>79,8%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>187437</t>
+          <t>188307</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>208676</t>
+          <t>208685</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>74,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>373857</t>
+          <t>374315</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>403847</t>
+          <t>404145</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>74,03%</t>
+          <t>74,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>80,03%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>575</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5701</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>553</t>
+          <t>555</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5258</t>
+          <t>5126</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1702</t>
+          <t>1355</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7732</t>
+          <t>8310</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17953</t>
+          <t>18092</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33001</t>
+          <t>32343</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28016</t>
+          <t>27174</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43866</t>
+          <t>43955</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>49774</t>
+          <t>49686</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>70130</t>
+          <t>71557</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,8%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>90598</t>
+          <t>90545</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>105564</t>
+          <t>105990</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>72,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>84,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>95690</t>
+          <t>95446</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>112037</t>
+          <t>112537</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>191763</t>
+          <t>191094</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>213563</t>
+          <t>213794</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>71,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>80,06%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>629</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5917</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>703</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7390</t>
+          <t>7082</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2066</t>
+          <t>2031</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9177</t>
+          <t>9383</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29514</t>
+          <t>29713</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>47270</t>
+          <t>47011</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>25737</t>
+          <t>25476</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>42379</t>
+          <t>41529</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>59623</t>
+          <t>57798</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>83973</t>
+          <t>82716</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>20,84%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>142979</t>
+          <t>142999</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>160968</t>
+          <t>160747</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>74,46%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>159410</t>
+          <t>160350</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>176914</t>
+          <t>176837</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>78,27%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>308013</t>
+          <t>308544</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>333207</t>
+          <t>334433</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>84,26%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>9416</t>
+          <t>8796</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>20927</t>
+          <t>20996</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>9022</t>
+          <t>9016</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>21127</t>
+          <t>21544</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>20730</t>
+          <t>20883</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>37295</t>
+          <t>38157</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>146738</t>
+          <t>146346</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>182586</t>
+          <t>182479</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>154862</t>
+          <t>155237</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>191573</t>
+          <t>191514</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>312048</t>
+          <t>310892</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>362266</t>
+          <t>362724</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>26,01%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>477467</t>
+          <t>478826</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>514381</t>
+          <t>515681</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>511759</t>
+          <t>513998</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>550048</t>
+          <t>550329</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>71,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1003068</t>
+          <t>1002908</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1055854</t>
+          <t>1055340</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>71,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>75,67%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5004</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15489</t>
+          <t>15103</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7795</t>
+          <t>7397</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19036</t>
+          <t>19009</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15514</t>
+          <t>14908</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30940</t>
+          <t>30342</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,39%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>57747</t>
+          <t>57823</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>77385</t>
+          <t>76271</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>49694</t>
+          <t>50663</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>70005</t>
+          <t>69787</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>48,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>112806</t>
+          <t>113025</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>139778</t>
+          <t>139727</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>47,84%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>60277</t>
+          <t>61506</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>80339</t>
+          <t>80574</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>54,74%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62532</t>
+          <t>64134</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>83482</t>
+          <t>83111</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>57,19%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>130202</t>
+          <t>130990</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>158738</t>
+          <t>157954</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>44,85%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>54,08%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1673</t>
+          <t>1587</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8768</t>
+          <t>9137</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7101</t>
+          <t>7305</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3756,7 +3756,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3786</t>
+          <t>3977</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>12458</t>
+          <t>13392</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>46874</t>
+          <t>45672</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>66777</t>
+          <t>67572</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>56895</t>
+          <t>56532</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>80882</t>
+          <t>81574</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>109309</t>
+          <t>108604</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>141387</t>
+          <t>141929</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,14%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>164102</t>
+          <t>163483</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>185631</t>
+          <t>186049</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>69,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>78,84%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>184506</t>
+          <t>184114</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>209350</t>
+          <t>208728</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>68,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>355835</t>
+          <t>355121</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>388432</t>
+          <t>388520</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>70,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>77,02%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>475</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6075</t>
+          <t>6177</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7326</t>
+          <t>7871</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2675</t>
+          <t>2631</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10784</t>
+          <t>10605</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23910</t>
+          <t>23700</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40207</t>
+          <t>39929</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28883</t>
+          <t>29462</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46878</t>
+          <t>46458</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>57168</t>
+          <t>57578</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>81725</t>
+          <t>81338</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,83%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>113827</t>
+          <t>113489</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>130584</t>
+          <t>130857</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>72,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>83,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>108262</t>
+          <t>108571</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>126856</t>
+          <t>126155</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>68,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>228060</t>
+          <t>228726</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>252688</t>
+          <t>252142</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>72,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>80,06%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>610</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6058</t>
+          <t>5943</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>726</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6813</t>
+          <t>6809</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,7 +4663,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1963</t>
+          <t>1974</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9903</t>
+          <t>8839</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20190</t>
+          <t>19336</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>36067</t>
+          <t>35143</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20315</t>
+          <t>20187</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>35890</t>
+          <t>36041</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>44286</t>
+          <t>44356</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>66933</t>
+          <t>65275</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>18,62%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>132946</t>
+          <t>133715</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>149284</t>
+          <t>150270</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>140616</t>
+          <t>140722</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>157046</t>
+          <t>156360</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>78,49%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>279889</t>
+          <t>280236</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>302745</t>
+          <t>302652</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,32%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11459</t>
+          <t>11417</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>25823</t>
+          <t>24964</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>15772</t>
+          <t>15187</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>29831</t>
+          <t>31094</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>30103</t>
+          <t>29396</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>51410</t>
+          <t>50495</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>162579</t>
+          <t>161945</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>200260</t>
+          <t>200562</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>172062</t>
+          <t>173928</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>212520</t>
+          <t>214090</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>343734</t>
+          <t>345473</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>398703</t>
+          <t>402882</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,56%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>490168</t>
+          <t>491483</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>529356</t>
+          <t>531483</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>69,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>517703</t>
+          <t>516931</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>559539</t>
+          <t>557348</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>68,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1022475</t>
+          <t>1019954</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1079630</t>
+          <t>1078025</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>73,73%</t>
         </is>
       </c>
     </row>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3340</t>
+          <t>2987</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10488</t>
+          <t>10590</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1824</t>
+          <t>1829</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8253</t>
+          <t>7614</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5423</t>
+          <t>5841</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15063</t>
+          <t>15033</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51552</t>
+          <t>51462</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>69378</t>
+          <t>69533</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,63%</t>
+          <t>53,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>54679</t>
+          <t>54491</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>72257</t>
+          <t>72431</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>58,45%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>110555</t>
+          <t>111425</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>137229</t>
+          <t>137412</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,24%</t>
+          <t>54,31%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>53800</t>
+          <t>53865</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>71123</t>
+          <t>72097</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>55,73%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>47680</t>
+          <t>47183</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>64810</t>
+          <t>64813</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,7 +6033,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>106449</t>
+          <t>106309</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>131836</t>
+          <t>131164</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>42,07%</t>
+          <t>42,02%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>51,84%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1189</t>
+          <t>1207</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8580</t>
+          <t>8399</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>1328</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>7892</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3600</t>
+          <t>3644</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>12846</t>
+          <t>12748</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>54350</t>
+          <t>55074</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>75045</t>
+          <t>76685</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>82698</t>
+          <t>84462</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>108707</t>
+          <t>109631</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>42,59%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>145043</t>
+          <t>146369</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>178190</t>
+          <t>177163</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>38,05%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>129900</t>
+          <t>127681</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>151288</t>
+          <t>149733</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>61,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>71,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>145083</t>
+          <t>144240</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>171702</t>
+          <t>170184</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>56,36%</t>
+          <t>56,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>66,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>279164</t>
+          <t>281584</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>313620</t>
+          <t>312889</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>67,19%</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>575</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5604</t>
+          <t>5481</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6336</t>
+          <t>6457</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2369</t>
+          <t>2425</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9116</t>
+          <t>9022</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40317</t>
+          <t>40765</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>60428</t>
+          <t>60320</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37550</t>
+          <t>36274</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>57150</t>
+          <t>56286</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>82510</t>
+          <t>82872</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>109921</t>
+          <t>110336</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,37%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>126018</t>
+          <t>126551</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>146266</t>
+          <t>146563</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,71%</t>
+          <t>66,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>127174</t>
+          <t>128060</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>147141</t>
+          <t>148130</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>68,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>79,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>260775</t>
+          <t>259956</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>288831</t>
+          <t>287781</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>69,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>76,61%</t>
         </is>
       </c>
     </row>
@@ -7165,7 +7165,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5132</t>
+          <t>5215</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>514</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5589</t>
+          <t>5335</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7215,7 +7215,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22804</t>
+          <t>23464</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39681</t>
+          <t>40712</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18658</t>
+          <t>18836</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34958</t>
+          <t>35019</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>46019</t>
+          <t>46562</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>69539</t>
+          <t>68877</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,07%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>132579</t>
+          <t>131755</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>149750</t>
+          <t>148868</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>133935</t>
+          <t>133486</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>150488</t>
+          <t>150264</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>78,31%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>271700</t>
+          <t>271427</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>295314</t>
+          <t>294184</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>85,71%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7642</t>
+          <t>7578</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>18865</t>
+          <t>19089</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7175</t>
+          <t>6835</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>18438</t>
+          <t>17898</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>16830</t>
+          <t>16195</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>31855</t>
+          <t>31552</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>186700</t>
+          <t>188877</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>225389</t>
+          <t>226691</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>212308</t>
+          <t>212559</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>253233</t>
+          <t>254974</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>414722</t>
+          <t>412495</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>472665</t>
+          <t>468156</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>32,57%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>461446</t>
+          <t>458336</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>500446</t>
+          <t>497620</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>474082</t>
+          <t>472693</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>515200</t>
+          <t>515355</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>69,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>939878</t>
+          <t>945678</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>999255</t>
+          <t>1002204</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>69,72%</t>
         </is>
       </c>
     </row>
@@ -8274,7 +8274,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3184</t>
+          <t>2726</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8289,7 +8289,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>408</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5988</t>
+          <t>6179</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8319,12 +8319,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1211</t>
+          <t>872</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7257</t>
+          <t>7346</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8354,12 +8354,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -8382,12 +8382,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>37491</t>
+          <t>37909</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47030</t>
+          <t>46988</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8397,12 +8397,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,7%</t>
+          <t>66,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36235</t>
+          <t>36461</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47377</t>
+          <t>47433</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8432,12 +8432,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,97%</t>
+          <t>59,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>77,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>77055</t>
+          <t>76812</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>91952</t>
+          <t>91466</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8467,12 +8467,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,02%</t>
+          <t>64,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>77,18%</t>
         </is>
       </c>
     </row>
@@ -8495,12 +8495,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9170</t>
+          <t>9396</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18588</t>
+          <t>18474</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8510,12 +8510,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12238</t>
+          <t>12435</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22856</t>
+          <t>23098</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>23664</t>
+          <t>23965</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>38120</t>
+          <t>38135</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,18%</t>
         </is>
       </c>
     </row>
@@ -8730,7 +8730,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5456</t>
+          <t>5839</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8745,7 +8745,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8800,7 +8800,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5960</t>
+          <t>5703</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8815,7 +8815,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -8838,12 +8838,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>46579</t>
+          <t>46535</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>66317</t>
+          <t>65371</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8853,12 +8853,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>41,04%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>54137</t>
+          <t>53711</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>76175</t>
+          <t>76342</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8888,12 +8888,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>105277</t>
+          <t>107020</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>135934</t>
+          <t>136495</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8923,12 +8923,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>39,93%</t>
         </is>
       </c>
     </row>
@@ -8951,12 +8951,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>91164</t>
+          <t>91508</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>111810</t>
+          <t>110962</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8966,12 +8966,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>57,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>69,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>106379</t>
+          <t>106212</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>128417</t>
+          <t>128843</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9001,12 +9001,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>58,27%</t>
+          <t>58,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>70,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>203998</t>
+          <t>204117</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>234453</t>
+          <t>233587</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9036,12 +9036,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,67%</t>
+          <t>59,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>68,33%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>806</t>
+          <t>807</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7415</t>
+          <t>6761</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>815</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7208</t>
+          <t>6737</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9271,7 +9271,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -9294,12 +9294,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30028</t>
+          <t>29691</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50896</t>
+          <t>51576</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>51556</t>
+          <t>50912</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>76364</t>
+          <t>77149</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9344,12 +9344,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>85655</t>
+          <t>85842</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>118752</t>
+          <t>118664</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,91%</t>
         </is>
       </c>
     </row>
@@ -9407,12 +9407,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>119627</t>
+          <t>119715</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>140710</t>
+          <t>141193</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9422,12 +9422,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>134525</t>
+          <t>133740</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>159333</t>
+          <t>159977</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9457,12 +9457,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>63,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>75,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>261015</t>
+          <t>262541</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>294800</t>
+          <t>295641</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>77,0%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1256</t>
+          <t>1218</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8757</t>
+          <t>8918</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1847</t>
+          <t>1844</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14742</t>
+          <t>14197</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4547</t>
+          <t>4557</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18112</t>
+          <t>18689</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9727,7 +9727,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -9750,12 +9750,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30071</t>
+          <t>30169</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>56216</t>
+          <t>56181</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9785,12 +9785,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>39303</t>
+          <t>38866</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>67364</t>
+          <t>68357</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9800,12 +9800,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>77424</t>
+          <t>76845</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>115555</t>
+          <t>117421</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9835,12 +9835,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,41%</t>
         </is>
       </c>
     </row>
@@ -9863,12 +9863,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>209181</t>
+          <t>209121</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>237180</t>
+          <t>237476</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9878,12 +9878,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>77,39%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9898,12 +9898,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>231963</t>
+          <t>231030</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>260951</t>
+          <t>262154</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>449713</t>
+          <t>447259</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>491027</t>
+          <t>490104</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>77,74%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>85,19%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4663</t>
+          <t>4474</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15615</t>
+          <t>14902</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3610</t>
+          <t>3613</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>17103</t>
+          <t>18565</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>10260</t>
+          <t>10404</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>26964</t>
+          <t>27234</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -10206,12 +10206,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>154090</t>
+          <t>156452</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>204120</t>
+          <t>203213</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>199124</t>
+          <t>198071</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>247200</t>
+          <t>247350</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10276,12 +10276,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>368954</t>
+          <t>369573</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>440360</t>
+          <t>434975</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10291,12 +10291,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>30,64%</t>
         </is>
       </c>
     </row>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>447035</t>
+          <t>447861</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>496594</t>
+          <t>495758</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>67,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>503401</t>
+          <t>504217</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>552053</t>
+          <t>554632</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10389,12 +10389,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>963471</t>
+          <t>967512</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1034488</t>
+          <t>1032773</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10404,12 +10404,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>68,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>72,75%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ23_R2-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ23_R2-Edad-trans_orig.xlsx
@@ -726,213 +726,213 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>5934</v>
+        <v>53990</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>2661</v>
+        <v>44817</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>10245</v>
+        <v>62060</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.04947839983231052</v>
+        <v>0.450148657532973</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.02218354083984312</v>
+        <v>0.3736684489889158</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.08541613476969465</v>
+        <v>0.5174284602658831</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>6195</v>
+        <v>44062</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>3096</v>
+        <v>35997</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>10865</v>
+        <v>52504</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.05859266456066951</v>
+        <v>0.4167677987812212</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.02928188054921929</v>
+        <v>0.3404868633650741</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.1027643291944101</v>
+        <v>0.4966158722971131</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>19</v>
+        <v>149</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>12129</v>
+        <v>98052</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>7624</v>
+        <v>86757</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>17942</v>
+        <v>110566</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.05374845689820047</v>
+        <v>0.4345096371592411</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0.033785070051008</v>
+        <v>0.3844559562890207</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.07950751371242898</v>
+        <v>0.4899627473809558</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>53990</v>
+        <v>60014</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>44817</v>
+        <v>51677</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>62060</v>
+        <v>69065</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.450148657532973</v>
+        <v>0.5003729426347164</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.3736684489889158</v>
+        <v>0.4308625836315129</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.5174284602658831</v>
+        <v>0.57583080460612</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>44062</v>
+        <v>55466</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>35997</v>
+        <v>47222</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>52504</v>
+        <v>64062</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.4167677987812212</v>
+        <v>0.5246395366581094</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.3404868633650741</v>
+        <v>0.4466610314092819</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.4966158722971131</v>
+        <v>0.6059415145889002</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>149</v>
+        <v>173</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>98052</v>
+        <v>115481</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>86757</v>
+        <v>104223</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>110566</v>
+        <v>127955</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.4345096371592411</v>
+        <v>0.5117419059425584</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.3844559562890207</v>
+        <v>0.4618555755383021</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.4899627473809558</v>
+        <v>0.5670203010186832</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>89</v>
+        <v>9</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>60014</v>
+        <v>5934</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>51677</v>
+        <v>2661</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>69065</v>
+        <v>10245</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.5003729426347164</v>
+        <v>0.04947839983231052</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.4308625836315129</v>
+        <v>0.02218354083984312</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.57583080460612</v>
+        <v>0.08541613476969465</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>84</v>
+        <v>10</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>55466</v>
+        <v>6195</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>47222</v>
+        <v>3096</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>64062</v>
+        <v>10865</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.5246395366581094</v>
+        <v>0.05859266456066951</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.4466610314092819</v>
+        <v>0.02928188054921929</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.6059415145889002</v>
+        <v>0.1027643291944101</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>173</v>
+        <v>19</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>115481</v>
+        <v>12129</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>104223</v>
+        <v>7624</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>127955</v>
+        <v>17942</v>
       </c>
       <c r="U6" s="6" t="n">
-        <v>0.5117419059425584</v>
+        <v>0.05374845689820047</v>
       </c>
       <c r="V6" s="6" t="n">
-        <v>0.4618555755383021</v>
+        <v>0.033785070051008</v>
       </c>
       <c r="W6" s="6" t="n">
-        <v>0.5670203010186832</v>
+        <v>0.07950751371242898</v>
       </c>
     </row>
     <row r="7">
@@ -1014,213 +1014,213 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>5</v>
+        <v>77</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>3281</v>
+        <v>51049</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>1260</v>
+        <v>41344</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>7227</v>
+        <v>61800</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.01295927187077959</v>
+        <v>0.2016523961983334</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.004976972370709608</v>
+        <v>0.1633145390426566</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.02854750968497538</v>
+        <v>0.244118843054064</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>7</v>
+        <v>87</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>4098</v>
+        <v>57109</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>1917</v>
+        <v>47361</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>7681</v>
+        <v>68767</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.01627440722430106</v>
+        <v>0.2267754433340113</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.007610610782395142</v>
+        <v>0.1880659342252196</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.03050216416532231</v>
+        <v>0.2730694505762188</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>12</v>
+        <v>164</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>7379</v>
+        <v>108158</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>3814</v>
+        <v>93399</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>12185</v>
+        <v>123811</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.01461249839165025</v>
+        <v>0.2141810212409481</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.007553245270641265</v>
+        <v>0.1849535570485085</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.0241289018258813</v>
+        <v>0.2451771996153171</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>77</v>
+        <v>299</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>51049</v>
+        <v>198824</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>41344</v>
+        <v>188192</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>61800</v>
+        <v>208822</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.2016523961983334</v>
+        <v>0.785388331930887</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.1633145390426566</v>
+        <v>0.743388204994365</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.244118843054064</v>
+        <v>0.8248818044200634</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>87</v>
+        <v>283</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>57109</v>
+        <v>190624</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>47361</v>
+        <v>178931</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>68767</v>
+        <v>201197</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.2267754433340113</v>
+        <v>0.7569501494416876</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.1880659342252196</v>
+        <v>0.7105207231777921</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.2730694505762188</v>
+        <v>0.7989358196933355</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>164</v>
+        <v>582</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>108158</v>
+        <v>389448</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>93399</v>
+        <v>373065</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>123811</v>
+        <v>403738</v>
       </c>
       <c r="U9" s="6" t="n">
-        <v>0.2141810212409481</v>
+        <v>0.7712064803674017</v>
       </c>
       <c r="V9" s="6" t="n">
-        <v>0.1849535570485085</v>
+        <v>0.7387643727306292</v>
       </c>
       <c r="W9" s="6" t="n">
-        <v>0.2451771996153171</v>
+        <v>0.7995053402179287</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>299</v>
+        <v>5</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>198824</v>
+        <v>3281</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>188192</v>
+        <v>1260</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>208822</v>
+        <v>7227</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.785388331930887</v>
+        <v>0.01295927187077959</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.743388204994365</v>
+        <v>0.004976972370709608</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.8248818044200634</v>
+        <v>0.02854750968497538</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>283</v>
+        <v>7</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>190624</v>
+        <v>4098</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>178931</v>
+        <v>1917</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>201197</v>
+        <v>7681</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.7569501494416876</v>
+        <v>0.01627440722430106</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.7105207231777921</v>
+        <v>0.007610610782395142</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.7989358196933355</v>
+        <v>0.03050216416532231</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>582</v>
+        <v>12</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>389448</v>
+        <v>7379</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>373065</v>
+        <v>3814</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>403738</v>
+        <v>12185</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.7712064803674017</v>
+        <v>0.01461249839165025</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.7387643727306292</v>
+        <v>0.007553245270641265</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.7995053402179287</v>
+        <v>0.0241289018258813</v>
       </c>
     </row>
     <row r="11">
@@ -1302,213 +1302,213 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>1855</v>
+        <v>35293</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>554</v>
+        <v>27256</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>4885</v>
+        <v>43649</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.0131098537318957</v>
+        <v>0.249393996170265</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.003914239064957487</v>
+        <v>0.192604942747373</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.03451901126944532</v>
+        <v>0.3084433505480614</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>1975</v>
+        <v>24799</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>574</v>
+        <v>18052</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>5951</v>
+        <v>32802</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.01573675951220061</v>
+        <v>0.1975564645363108</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.004574259913096674</v>
+        <v>0.1438096940986588</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.04740887809196106</v>
+        <v>0.2613137355171669</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>6</v>
+        <v>92</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>3831</v>
+        <v>60092</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>1362</v>
+        <v>50690</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>8044</v>
+        <v>71025</v>
       </c>
       <c r="U12" s="6" t="n">
-        <v>0.01434468008859404</v>
+        <v>0.2250267916790704</v>
       </c>
       <c r="V12" s="6" t="n">
-        <v>0.005099628983357151</v>
+        <v>0.1898191251496288</v>
       </c>
       <c r="W12" s="6" t="n">
-        <v>0.03012324516816817</v>
+        <v>0.2659661071060809</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>54</v>
+        <v>155</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>35293</v>
+        <v>104367</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>27256</v>
+        <v>95406</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>43649</v>
+        <v>112099</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.249393996170265</v>
+        <v>0.7374961500978393</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.192604942747373</v>
+        <v>0.6741729946960164</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.3084433505480614</v>
+        <v>0.7921371258835969</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>38</v>
+        <v>147</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>24799</v>
+        <v>98755</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>18052</v>
+        <v>91279</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>32802</v>
+        <v>105814</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.1975564645363108</v>
+        <v>0.7867067759514885</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.1438096940986588</v>
+        <v>0.7271577690746183</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.2613137355171669</v>
+        <v>0.8429462603963471</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>92</v>
+        <v>302</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>60092</v>
+        <v>203121</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>50690</v>
+        <v>192173</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>71025</v>
+        <v>213007</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.2250267916790704</v>
+        <v>0.7606285282323355</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.1898191251496288</v>
+        <v>0.7196317172911815</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.2659661071060809</v>
+        <v>0.7976460294125479</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>155</v>
+        <v>3</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>104367</v>
+        <v>1855</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>95406</v>
+        <v>554</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>112099</v>
+        <v>4885</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.7374961500978393</v>
+        <v>0.0131098537318957</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.6741729946960164</v>
+        <v>0.003914239064957487</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.7921371258835969</v>
+        <v>0.03451901126944532</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>147</v>
+        <v>3</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>98755</v>
+        <v>1975</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>91279</v>
+        <v>574</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>105814</v>
+        <v>5951</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.7867067759514885</v>
+        <v>0.01573675951220061</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.7271577690746183</v>
+        <v>0.004574259913096674</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.8429462603963471</v>
+        <v>0.04740887809196106</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>302</v>
+        <v>6</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>203121</v>
+        <v>3831</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>192173</v>
+        <v>1362</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>213007</v>
+        <v>8044</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.7606285282323355</v>
+        <v>0.01434468008859404</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.7196317172911815</v>
+        <v>0.005099628983357151</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.7976460294125479</v>
+        <v>0.03012324516816817</v>
       </c>
     </row>
     <row r="15">
@@ -1590,213 +1590,213 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>2883</v>
+        <v>32826</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>711</v>
+        <v>25731</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>7213</v>
+        <v>42623</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.01407226648265206</v>
+        <v>0.1602255897660815</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.003470754533848467</v>
+        <v>0.1255945603500575</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.03520657714114405</v>
+        <v>0.2080502305147481</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>3</v>
+        <v>57</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>1954</v>
+        <v>37776</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>628</v>
+        <v>29087</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>5191</v>
+        <v>46996</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.01017559459050437</v>
+        <v>0.1966907298045109</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.003268009210855157</v>
+        <v>0.151447711497442</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.02702792096039822</v>
+        <v>0.2446983501002574</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>7</v>
+        <v>106</v>
       </c>
       <c r="R16" s="5" t="n">
-        <v>4837</v>
+        <v>70601</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>2118</v>
+        <v>58930</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>10238</v>
+        <v>84704</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.01218682846315095</v>
+        <v>0.1778695596249328</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.005335857993623975</v>
+        <v>0.1484654427180426</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.0257941899182349</v>
+        <v>0.213398486517594</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>49</v>
+        <v>255</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>32826</v>
+        <v>169162</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>25731</v>
+        <v>158885</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>42623</v>
+        <v>176826</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.1602255897660815</v>
+        <v>0.8257021437512664</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.1255945603500575</v>
+        <v>0.7755345177177253</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.2080502305147481</v>
+        <v>0.8631069250476203</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>57</v>
+        <v>223</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>37776</v>
+        <v>152327</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>29087</v>
+        <v>142776</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>46996</v>
+        <v>161432</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.1966907298045109</v>
+        <v>0.7931336756049848</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.151447711497442</v>
+        <v>0.7434023092494614</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.2446983501002574</v>
+        <v>0.8405397642801484</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>106</v>
+        <v>478</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>70601</v>
+        <v>321489</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>58930</v>
+        <v>307156</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>84704</v>
+        <v>333579</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.1778695596249328</v>
+        <v>0.8099436119119162</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.1484654427180426</v>
+        <v>0.7738318564928003</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.213398486517594</v>
+        <v>0.8404009718197619</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>255</v>
+        <v>4</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>169162</v>
+        <v>2883</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>158885</v>
+        <v>711</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>176826</v>
+        <v>7213</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.8257021437512664</v>
+        <v>0.01407226648265206</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.7755345177177253</v>
+        <v>0.003470754533848467</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.8631069250476203</v>
+        <v>0.03520657714114405</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>223</v>
+        <v>3</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>152327</v>
+        <v>1954</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>142776</v>
+        <v>628</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>161432</v>
+        <v>5191</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.7931336756049848</v>
+        <v>0.01017559459050437</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.7434023092494614</v>
+        <v>0.003268009210855157</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.8405397642801484</v>
+        <v>0.02702792096039822</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>478</v>
+        <v>7</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>321489</v>
+        <v>4837</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>307156</v>
+        <v>2118</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>333579</v>
+        <v>10238</v>
       </c>
       <c r="U18" s="6" t="n">
-        <v>0.8099436119119162</v>
+        <v>0.01218682846315095</v>
       </c>
       <c r="V18" s="6" t="n">
-        <v>0.7738318564928003</v>
+        <v>0.005335857993623975</v>
       </c>
       <c r="W18" s="6" t="n">
-        <v>0.8404009718197619</v>
+        <v>0.0257941899182349</v>
       </c>
     </row>
     <row r="19">
@@ -1878,213 +1878,213 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>21</v>
+        <v>262</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>13953</v>
+        <v>173158</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>8673</v>
+        <v>155077</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>20533</v>
+        <v>192328</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.01939364606044573</v>
+        <v>0.2406714509904848</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.01205389154463701</v>
+        <v>0.2155405004282913</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.02853808152769957</v>
+        <v>0.2673151057545288</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>23</v>
+        <v>249</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>14223</v>
+        <v>163746</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>8940</v>
+        <v>146150</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>20426</v>
+        <v>181168</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.02106632777329644</v>
+        <v>0.2425363542128633</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.01324141891628579</v>
+        <v>0.2164728860574858</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.03025468291728948</v>
+        <v>0.2683416773859439</v>
       </c>
       <c r="Q20" s="5" t="n">
-        <v>44</v>
+        <v>511</v>
       </c>
       <c r="R20" s="5" t="n">
-        <v>28176</v>
+        <v>336904</v>
       </c>
       <c r="S20" s="5" t="n">
-        <v>20465</v>
+        <v>310418</v>
       </c>
       <c r="T20" s="5" t="n">
-        <v>37257</v>
+        <v>361950</v>
       </c>
       <c r="U20" s="6" t="n">
-        <v>0.0202033978295066</v>
+        <v>0.2415742579452369</v>
       </c>
       <c r="V20" s="6" t="n">
-        <v>0.01467404925083009</v>
+        <v>0.2225826143972093</v>
       </c>
       <c r="W20" s="6" t="n">
-        <v>0.0267145879247149</v>
+        <v>0.2595332328959067</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>262</v>
+        <v>798</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>173158</v>
+        <v>532368</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>155077</v>
+        <v>513235</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>192328</v>
+        <v>551237</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.2406714509904848</v>
+        <v>0.7399349029490695</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.2155405004282913</v>
+        <v>0.7133427101810375</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.2673151057545288</v>
+        <v>0.7661608922029639</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>249</v>
+        <v>737</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>163746</v>
+        <v>497172</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>146150</v>
+        <v>480522</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>181168</v>
+        <v>515664</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.2425363542128633</v>
+        <v>0.7363973180138402</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.2164728860574858</v>
+        <v>0.7117351437053366</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.2683416773859439</v>
+        <v>0.7637877192766752</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>511</v>
+        <v>1535</v>
       </c>
       <c r="R21" s="5" t="n">
-        <v>336904</v>
+        <v>1029540</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>310418</v>
+        <v>1003723</v>
       </c>
       <c r="T21" s="5" t="n">
-        <v>361950</v>
+        <v>1057093</v>
       </c>
       <c r="U21" s="6" t="n">
-        <v>0.2415742579452369</v>
+        <v>0.7382223442252565</v>
       </c>
       <c r="V21" s="6" t="n">
-        <v>0.2225826143972093</v>
+        <v>0.7197107979666113</v>
       </c>
       <c r="W21" s="6" t="n">
-        <v>0.2595332328959067</v>
+        <v>0.7579792910117095</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n"/>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>798</v>
+        <v>21</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>532368</v>
+        <v>13953</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>513235</v>
+        <v>8673</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>551237</v>
+        <v>20533</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.7399349029490695</v>
+        <v>0.01939364606044573</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.7133427101810375</v>
+        <v>0.01205389154463701</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.7661608922029639</v>
+        <v>0.02853808152769957</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>737</v>
+        <v>23</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>497172</v>
+        <v>14223</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>480522</v>
+        <v>8940</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>515664</v>
+        <v>20426</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.7363973180138402</v>
+        <v>0.02106632777329644</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.7117351437053366</v>
+        <v>0.01324141891628579</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.7637877192766752</v>
+        <v>0.03025468291728948</v>
       </c>
       <c r="Q22" s="5" t="n">
-        <v>1535</v>
+        <v>44</v>
       </c>
       <c r="R22" s="5" t="n">
-        <v>1029540</v>
+        <v>28176</v>
       </c>
       <c r="S22" s="5" t="n">
-        <v>1003723</v>
+        <v>20465</v>
       </c>
       <c r="T22" s="5" t="n">
-        <v>1057093</v>
+        <v>37257</v>
       </c>
       <c r="U22" s="6" t="n">
-        <v>0.7382223442252565</v>
+        <v>0.0202033978295066</v>
       </c>
       <c r="V22" s="6" t="n">
-        <v>0.7197107979666113</v>
+        <v>0.01467404925083009</v>
       </c>
       <c r="W22" s="6" t="n">
-        <v>0.7579792910117095</v>
+        <v>0.0267145879247149</v>
       </c>
     </row>
     <row r="23">
@@ -2398,213 +2398,213 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>12373</v>
+        <v>60085</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>7473</v>
+        <v>50022</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>19138</v>
+        <v>70463</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.0851423427896538</v>
+        <v>0.4134593237623926</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.05142226266334124</v>
+        <v>0.3442170737558362</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.1316923777241535</v>
+        <v>0.4848747896071831</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>9132</v>
+        <v>66725</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>4764</v>
+        <v>56344</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>14702</v>
+        <v>76912</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.06222135434755188</v>
+        <v>0.454651394334957</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.03246058258976858</v>
+        <v>0.3839140051603254</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.1001734021152605</v>
+        <v>0.5240601255146776</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>30</v>
+        <v>188</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>21505</v>
+        <v>126810</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>14440</v>
+        <v>112279</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>30071</v>
+        <v>139155</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.07362539104617102</v>
+        <v>0.4341568207397462</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0.04943968299017897</v>
+        <v>0.3844082542090262</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.102951943516764</v>
+        <v>0.4764225227983071</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>60085</v>
+        <v>72864</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>50022</v>
+        <v>62261</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>70463</v>
+        <v>83204</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.4134593237623926</v>
+        <v>0.5013983334479536</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.3442170737558362</v>
+        <v>0.4284355903817771</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.4848747896071831</v>
+        <v>0.5725506355482149</v>
       </c>
       <c r="J5" s="5" t="n">
         <v>103</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>66725</v>
+        <v>70904</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>56344</v>
+        <v>59805</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>76912</v>
+        <v>81309</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.454651394334957</v>
+        <v>0.4831272513174911</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.3839140051603254</v>
+        <v>0.4074985145480798</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.5240601255146776</v>
+        <v>0.5540253725411372</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>188</v>
+        <v>207</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>126810</v>
+        <v>143768</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>112279</v>
+        <v>130425</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>139155</v>
+        <v>158170</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.4341568207397462</v>
+        <v>0.4922177882140828</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.3844082542090262</v>
+        <v>0.4465331060624804</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.4764225227983071</v>
+        <v>0.5415231709301719</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>104</v>
+        <v>17</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>72864</v>
+        <v>12373</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>62261</v>
+        <v>7473</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>83204</v>
+        <v>19138</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.5013983334479536</v>
+        <v>0.0851423427896538</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.4284355903817771</v>
+        <v>0.05142226266334124</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.5725506355482149</v>
+        <v>0.1316923777241535</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>70904</v>
+        <v>9132</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>59805</v>
+        <v>4764</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>81309</v>
+        <v>14702</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.4831272513174911</v>
+        <v>0.06222135434755188</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.4074985145480798</v>
+        <v>0.03246058258976858</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.5540253725411372</v>
+        <v>0.1001734021152605</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>207</v>
+        <v>30</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>143768</v>
+        <v>21505</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>130425</v>
+        <v>14440</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>158170</v>
+        <v>30071</v>
       </c>
       <c r="U6" s="6" t="n">
-        <v>0.4922177882140828</v>
+        <v>0.07362539104617102</v>
       </c>
       <c r="V6" s="6" t="n">
-        <v>0.4465331060624804</v>
+        <v>0.04943968299017897</v>
       </c>
       <c r="W6" s="6" t="n">
-        <v>0.5415231709301719</v>
+        <v>0.102951943516764</v>
       </c>
     </row>
     <row r="7">
@@ -2686,213 +2686,213 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>5</v>
+        <v>97</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>3299</v>
+        <v>68537</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>1280</v>
+        <v>57150</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>7255</v>
+        <v>80705</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.01226455526235464</v>
+        <v>0.2547922885541908</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.004756706394814103</v>
+        <v>0.2124595111328448</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.02697300611929875</v>
+        <v>0.3000302398602125</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>6</v>
+        <v>81</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>4122</v>
+        <v>56505</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>1624</v>
+        <v>46458</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>8959</v>
+        <v>67797</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.01750554004114772</v>
+        <v>0.2399749209926482</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.006897700122312271</v>
+        <v>0.1973038998092253</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.03804706436436998</v>
+        <v>0.2879317390073313</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>11</v>
+        <v>178</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>7421</v>
+        <v>125042</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>4038</v>
+        <v>109224</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>13754</v>
+        <v>141355</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.01471088162076455</v>
+        <v>0.2478760088170844</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.008005493489952279</v>
+        <v>0.2165185876804485</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.02726487222187348</v>
+        <v>0.2802126854152354</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>97</v>
+        <v>272</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>68537</v>
+        <v>197155</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>57150</v>
+        <v>184732</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>80705</v>
+        <v>209118</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.2547922885541908</v>
+        <v>0.7329431561834545</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.2124595111328448</v>
+        <v>0.6867602960734188</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.3000302398602125</v>
+        <v>0.7774152395949341</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>81</v>
+        <v>252</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>56505</v>
+        <v>174836</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>46458</v>
+        <v>163567</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>67797</v>
+        <v>185446</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.2399749209926482</v>
+        <v>0.742519538966204</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.1973038998092253</v>
+        <v>0.694661566820068</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.2879317390073313</v>
+        <v>0.7875786034888536</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>178</v>
+        <v>524</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>125042</v>
+        <v>371992</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>109224</v>
+        <v>355582</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>141355</v>
+        <v>388552</v>
       </c>
       <c r="U9" s="6" t="n">
-        <v>0.2478760088170844</v>
+        <v>0.737413109562151</v>
       </c>
       <c r="V9" s="6" t="n">
-        <v>0.2165185876804485</v>
+        <v>0.7048835895342406</v>
       </c>
       <c r="W9" s="6" t="n">
-        <v>0.2802126854152354</v>
+        <v>0.7702408255460588</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>272</v>
+        <v>5</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>197155</v>
+        <v>3299</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>184732</v>
+        <v>1280</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>209118</v>
+        <v>7255</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.7329431561834545</v>
+        <v>0.01226455526235464</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.6867602960734188</v>
+        <v>0.004756706394814103</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.7774152395949341</v>
+        <v>0.02697300611929875</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>252</v>
+        <v>6</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>174836</v>
+        <v>4122</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>163567</v>
+        <v>1624</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>185446</v>
+        <v>8959</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.742519538966204</v>
+        <v>0.01750554004114772</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.694661566820068</v>
+        <v>0.006897700122312271</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.7875786034888536</v>
+        <v>0.03804706436436998</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>524</v>
+        <v>11</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>371992</v>
+        <v>7421</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>355582</v>
+        <v>4038</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>388552</v>
+        <v>13754</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.737413109562151</v>
+        <v>0.01471088162076455</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.7048835895342406</v>
+        <v>0.008005493489952279</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.7702408255460588</v>
+        <v>0.02726487222187348</v>
       </c>
     </row>
     <row r="11">
@@ -2974,213 +2974,213 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>3311</v>
+        <v>37052</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>703</v>
+        <v>28915</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>6904</v>
+        <v>46674</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.02088074425773104</v>
+        <v>0.2336622958830362</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.004430245003437553</v>
+        <v>0.1823502798734106</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.04353929268392868</v>
+        <v>0.2943393715021645</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>2139</v>
+        <v>31121</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>477</v>
+        <v>23204</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>6727</v>
+        <v>39519</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.01368186982820246</v>
+        <v>0.1990211590900663</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.003053217327777977</v>
+        <v>0.1483908394740822</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.04302285525851925</v>
+        <v>0.252731768891312</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>8</v>
+        <v>99</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>5450</v>
+        <v>68173</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>2587</v>
+        <v>55882</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>10342</v>
+        <v>80616</v>
       </c>
       <c r="U12" s="6" t="n">
-        <v>0.01730648611716478</v>
+        <v>0.2164628897268643</v>
       </c>
       <c r="V12" s="6" t="n">
-        <v>0.00821466567960182</v>
+        <v>0.1774364699671281</v>
       </c>
       <c r="W12" s="6" t="n">
-        <v>0.03283723845053527</v>
+        <v>0.2559730041563377</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>54</v>
+        <v>169</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>37052</v>
+        <v>118208</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>28915</v>
+        <v>107859</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>46674</v>
+        <v>126379</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.2336622958830362</v>
+        <v>0.7454569598592328</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.1823502798734106</v>
+        <v>0.6801935388653685</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.2943393715021645</v>
+        <v>0.7969871404727331</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>45</v>
+        <v>174</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>31121</v>
+        <v>123108</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>23204</v>
+        <v>114328</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>39519</v>
+        <v>130843</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.1990211590900663</v>
+        <v>0.7872969710817312</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.1483908394740822</v>
+        <v>0.7311492322015327</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.252731768891312</v>
+        <v>0.8367637606585518</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>99</v>
+        <v>343</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>68173</v>
+        <v>241316</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>55882</v>
+        <v>228602</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>80616</v>
+        <v>253716</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.2164628897268643</v>
+        <v>0.7662306241559709</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.1774364699671281</v>
+        <v>0.7258610233061979</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.2559730041563377</v>
+        <v>0.805604726929763</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>169</v>
+        <v>5</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>118208</v>
+        <v>3311</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>107859</v>
+        <v>703</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>126379</v>
+        <v>6904</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.7454569598592328</v>
+        <v>0.02088074425773104</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.6801935388653685</v>
+        <v>0.004430245003437553</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.7969871404727331</v>
+        <v>0.04353929268392868</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>174</v>
+        <v>3</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>123108</v>
+        <v>2139</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>114328</v>
+        <v>477</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>130843</v>
+        <v>6727</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.7872969710817312</v>
+        <v>0.01368186982820246</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.7311492322015327</v>
+        <v>0.003053217327777977</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.8367637606585518</v>
+        <v>0.04302285525851925</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>343</v>
+        <v>8</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>241316</v>
+        <v>5450</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>228602</v>
+        <v>2587</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>253716</v>
+        <v>10342</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.7662306241559709</v>
+        <v>0.01730648611716478</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.7258610233061979</v>
+        <v>0.00821466567960182</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.805604726929763</v>
+        <v>0.03283723845053527</v>
       </c>
     </row>
     <row r="15">
@@ -3262,213 +3262,213 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>2677</v>
+        <v>26882</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>665</v>
+        <v>19422</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>6869</v>
+        <v>34873</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.0149306962521439</v>
+        <v>0.1499391571491244</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.003710730011135309</v>
+        <v>0.1083289811897087</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.03831237574872132</v>
+        <v>0.1945082695865671</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>2063</v>
+        <v>27171</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>610</v>
+        <v>19136</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>5685</v>
+        <v>35866</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.01204211504353696</v>
+        <v>0.1585827832201779</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.003559495310535046</v>
+        <v>0.1116846244709024</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.03318290785977183</v>
+        <v>0.2093276968034928</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>7</v>
+        <v>77</v>
       </c>
       <c r="R16" s="5" t="n">
-        <v>4740</v>
+        <v>54053</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>1964</v>
+        <v>42758</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>9367</v>
+        <v>66087</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.01351915352400961</v>
+        <v>0.1541629773030994</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.005601944524545091</v>
+        <v>0.1219475257086044</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.02671472771009114</v>
+        <v>0.1884836760130168</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>39</v>
+        <v>221</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>26882</v>
+        <v>149728</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>19422</v>
+        <v>141402</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>34873</v>
+        <v>157299</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.1499391571491244</v>
+        <v>0.8351301465987317</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.1083289811897087</v>
+        <v>0.7886903750711852</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.1945082695865671</v>
+        <v>0.8773578563268539</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>38</v>
+        <v>202</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>27171</v>
+        <v>142103</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>19136</v>
+        <v>132985</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>35866</v>
+        <v>150080</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.1585827832201779</v>
+        <v>0.8293751017362851</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.1116846244709024</v>
+        <v>0.7761622871014084</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.2093276968034928</v>
+        <v>0.8759351476759397</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>77</v>
+        <v>423</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>54053</v>
+        <v>291831</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>42758</v>
+        <v>279666</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>66087</v>
+        <v>303689</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.1541629773030994</v>
+        <v>0.832317869172891</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.1219475257086044</v>
+        <v>0.7976223097663799</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.1884836760130168</v>
+        <v>0.8661382375765366</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>221</v>
+        <v>4</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>149728</v>
+        <v>2677</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>141402</v>
+        <v>665</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>157299</v>
+        <v>6869</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.8351301465987317</v>
+        <v>0.0149306962521439</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.7886903750711852</v>
+        <v>0.003710730011135309</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.8773578563268539</v>
+        <v>0.03831237574872132</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>202</v>
+        <v>3</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>142103</v>
+        <v>2063</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>132985</v>
+        <v>610</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>150080</v>
+        <v>5685</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.8293751017362851</v>
+        <v>0.01204211504353696</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.7761622871014084</v>
+        <v>0.003559495310535046</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.8759351476759397</v>
+        <v>0.03318290785977183</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>423</v>
+        <v>7</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>291831</v>
+        <v>4740</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>279666</v>
+        <v>1964</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>303689</v>
+        <v>9367</v>
       </c>
       <c r="U18" s="6" t="n">
-        <v>0.832317869172891</v>
+        <v>0.01351915352400961</v>
       </c>
       <c r="V18" s="6" t="n">
-        <v>0.7976223097663799</v>
+        <v>0.005601944524545091</v>
       </c>
       <c r="W18" s="6" t="n">
-        <v>0.8661382375765366</v>
+        <v>0.02671472771009114</v>
       </c>
     </row>
     <row r="19">
@@ -3550,213 +3550,213 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>31</v>
+        <v>275</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>21660</v>
+        <v>192556</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>15299</v>
+        <v>173788</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>31292</v>
+        <v>211642</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.0287967386144427</v>
+        <v>0.2560000077441857</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.02033989782050098</v>
+        <v>0.2310486856727014</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.04160258244750865</v>
+        <v>0.2813744590352787</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>25</v>
+        <v>267</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>17456</v>
+        <v>181522</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>11542</v>
+        <v>163119</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>25465</v>
+        <v>200197</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.02458870967016811</v>
+        <v>0.2556902739256171</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.0162584324010649</v>
+        <v>0.2297686792260264</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.03587048487263438</v>
+        <v>0.2819956789192741</v>
       </c>
       <c r="Q20" s="5" t="n">
-        <v>56</v>
+        <v>542</v>
       </c>
       <c r="R20" s="5" t="n">
-        <v>39116</v>
+        <v>374078</v>
       </c>
       <c r="S20" s="5" t="n">
-        <v>29395</v>
+        <v>346260</v>
       </c>
       <c r="T20" s="5" t="n">
-        <v>50222</v>
+        <v>399492</v>
       </c>
       <c r="U20" s="6" t="n">
-        <v>0.02675351171362498</v>
+        <v>0.2558496151307856</v>
       </c>
       <c r="V20" s="6" t="n">
-        <v>0.0201045068602867</v>
+        <v>0.236823849601798</v>
       </c>
       <c r="W20" s="6" t="n">
-        <v>0.03434890626967004</v>
+        <v>0.2732314695523477</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>275</v>
+        <v>766</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>192556</v>
+        <v>537955</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>173788</v>
+        <v>516946</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>211642</v>
+        <v>557406</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.2560000077441857</v>
+        <v>0.7152032536413716</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.2310486856727014</v>
+        <v>0.6872713674420108</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.2813744590352787</v>
+        <v>0.7410624134996078</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>267</v>
+        <v>731</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>181522</v>
+        <v>510951</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>163119</v>
+        <v>490900</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>200197</v>
+        <v>528676</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.2556902739256171</v>
+        <v>0.7197210164042148</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.2297686792260264</v>
+        <v>0.6914777132122374</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.2819956789192741</v>
+        <v>0.7446884119296957</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>542</v>
+        <v>1497</v>
       </c>
       <c r="R21" s="5" t="n">
-        <v>374078</v>
+        <v>1048906</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>346260</v>
+        <v>1019157</v>
       </c>
       <c r="T21" s="5" t="n">
-        <v>399492</v>
+        <v>1074094</v>
       </c>
       <c r="U21" s="6" t="n">
-        <v>0.2558496151307856</v>
+        <v>0.7173968731555894</v>
       </c>
       <c r="V21" s="6" t="n">
-        <v>0.236823849601798</v>
+        <v>0.6970501449409208</v>
       </c>
       <c r="W21" s="6" t="n">
-        <v>0.2732314695523477</v>
+        <v>0.7346239874790342</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n"/>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>766</v>
+        <v>31</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>537955</v>
+        <v>21660</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>516946</v>
+        <v>15299</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>557406</v>
+        <v>31292</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.7152032536413716</v>
+        <v>0.0287967386144427</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.6872713674420108</v>
+        <v>0.02033989782050098</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.7410624134996078</v>
+        <v>0.04160258244750865</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>731</v>
+        <v>25</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>510951</v>
+        <v>17456</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>490900</v>
+        <v>11542</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>528676</v>
+        <v>25465</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.7197210164042148</v>
+        <v>0.02458870967016811</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.6914777132122374</v>
+        <v>0.0162584324010649</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.7446884119296957</v>
+        <v>0.03587048487263438</v>
       </c>
       <c r="Q22" s="5" t="n">
-        <v>1497</v>
+        <v>56</v>
       </c>
       <c r="R22" s="5" t="n">
-        <v>1048906</v>
+        <v>39116</v>
       </c>
       <c r="S22" s="5" t="n">
-        <v>1019157</v>
+        <v>29395</v>
       </c>
       <c r="T22" s="5" t="n">
-        <v>1074094</v>
+        <v>50222</v>
       </c>
       <c r="U22" s="6" t="n">
-        <v>0.7173968731555894</v>
+        <v>0.02675351171362498</v>
       </c>
       <c r="V22" s="6" t="n">
-        <v>0.6970501449409208</v>
+        <v>0.0201045068602867</v>
       </c>
       <c r="W22" s="6" t="n">
-        <v>0.7346239874790342</v>
+        <v>0.03434890626967004</v>
       </c>
     </row>
     <row r="23">
@@ -4070,213 +4070,213 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>7</v>
+        <v>97</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>3810</v>
+        <v>63396</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>1334</v>
+        <v>54210</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>8005</v>
+        <v>72269</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.03082115897243374</v>
+        <v>0.5127809608286594</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.01079421656535602</v>
+        <v>0.4384829723239337</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.06474530731118364</v>
+        <v>0.5845535700985977</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>10</v>
+        <v>98</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>5829</v>
+        <v>60930</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>2980</v>
+        <v>52273</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>10630</v>
+        <v>70343</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.04506072283277585</v>
+        <v>0.470984986089155</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.02303868465944192</v>
+        <v>0.4040691380924284</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.08217173976077626</v>
+        <v>0.5437500788459314</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>17</v>
+        <v>195</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>9640</v>
+        <v>124326</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>5419</v>
+        <v>112702</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>15229</v>
+        <v>138669</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.03810236367743028</v>
+        <v>0.4914091652520577</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0.02141956307886813</v>
+        <v>0.4454643339578999</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.06019461333471213</v>
+        <v>0.5481025682327534</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>63396</v>
+        <v>56425</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>54210</v>
+        <v>47360</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>72269</v>
+        <v>65151</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.5127809608286594</v>
+        <v>0.4563978801989069</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.4384829723239337</v>
+        <v>0.3830762539581808</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.5845535700985977</v>
+        <v>0.5269767809234247</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>60930</v>
+        <v>62608</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>52273</v>
+        <v>53279</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>70343</v>
+        <v>71958</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.470984986089155</v>
+        <v>0.4839542910780692</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.4040691380924284</v>
+        <v>0.4118430294937581</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.5437500788459314</v>
+        <v>0.5562338286808242</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>124326</v>
+        <v>119033</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>112702</v>
+        <v>104862</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>138669</v>
+        <v>130679</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.4914091652520577</v>
+        <v>0.470488471070512</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.4454643339578999</v>
+        <v>0.4144744808260172</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.5481025682327534</v>
+        <v>0.5165195285362104</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>82</v>
+        <v>7</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>56425</v>
+        <v>3810</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>47360</v>
+        <v>1334</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>65151</v>
+        <v>8005</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.4563978801989069</v>
+        <v>0.03082115897243374</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.3830762539581808</v>
+        <v>0.01079421656535602</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.5269767809234247</v>
+        <v>0.06474530731118364</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>99</v>
+        <v>10</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>62608</v>
+        <v>5829</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>53279</v>
+        <v>2980</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>71958</v>
+        <v>10630</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.4839542910780692</v>
+        <v>0.04506072283277585</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.4118430294937581</v>
+        <v>0.02303868465944192</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.5562338286808242</v>
+        <v>0.08217173976077626</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>181</v>
+        <v>17</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>119033</v>
+        <v>9640</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>104862</v>
+        <v>5419</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>130679</v>
+        <v>15229</v>
       </c>
       <c r="U6" s="6" t="n">
-        <v>0.470488471070512</v>
+        <v>0.03810236367743028</v>
       </c>
       <c r="V6" s="6" t="n">
-        <v>0.4144744808260172</v>
+        <v>0.02141956307886813</v>
       </c>
       <c r="W6" s="6" t="n">
-        <v>0.5165195285362104</v>
+        <v>0.06019461333471213</v>
       </c>
     </row>
     <row r="7">
@@ -4358,213 +4358,213 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>3458</v>
+        <v>96779</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>1342</v>
+        <v>85606</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>8380</v>
+        <v>110727</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.01343319040843948</v>
+        <v>0.3759363602097867</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.005213290935540173</v>
+        <v>0.3325327284074402</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.03255165460078553</v>
+        <v>0.4301170485545499</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>5</v>
+        <v>103</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>3490</v>
+        <v>64553</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>1191</v>
+        <v>54971</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>8450</v>
+        <v>74835</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.01676421487535934</v>
+        <v>0.3100372749551656</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.005720877708856155</v>
+        <v>0.2640164975070309</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.04058242394332646</v>
+        <v>0.3594218414165414</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>10</v>
+        <v>242</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>6949</v>
+        <v>161332</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>3160</v>
+        <v>144041</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>11909</v>
+        <v>175821</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.01492263602966899</v>
+        <v>0.3464700188633703</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.006785597074754612</v>
+        <v>0.3093363350286479</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.02557632622089983</v>
+        <v>0.3775860879084753</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>139</v>
+        <v>235</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>96779</v>
+        <v>157198</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>85606</v>
+        <v>142831</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>110727</v>
+        <v>168474</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.3759363602097867</v>
+        <v>0.6106304493817738</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.3325327284074402</v>
+        <v>0.5548228340443621</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.4301170485545499</v>
+        <v>0.6544312728528292</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>103</v>
+        <v>220</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>64553</v>
+        <v>140167</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>54971</v>
+        <v>129614</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>74835</v>
+        <v>150455</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.3100372749551656</v>
+        <v>0.6731985101694751</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.2640164975070309</v>
+        <v>0.6225179847811173</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.3594218414165414</v>
+        <v>0.7226106036615243</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>242</v>
+        <v>455</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>161332</v>
+        <v>297364</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>144041</v>
+        <v>281917</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>175821</v>
+        <v>314180</v>
       </c>
       <c r="U9" s="6" t="n">
-        <v>0.3464700188633703</v>
+        <v>0.6386073451069607</v>
       </c>
       <c r="V9" s="6" t="n">
-        <v>0.3093363350286479</v>
+        <v>0.6054333595595206</v>
       </c>
       <c r="W9" s="6" t="n">
-        <v>0.3775860879084753</v>
+        <v>0.6747192082092355</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>235</v>
+        <v>5</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>157198</v>
+        <v>3458</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>142831</v>
+        <v>1342</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>168474</v>
+        <v>8380</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.6106304493817738</v>
+        <v>0.01343319040843948</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.5548228340443621</v>
+        <v>0.005213290935540173</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.6544312728528292</v>
+        <v>0.03255165460078553</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>220</v>
+        <v>5</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>140167</v>
+        <v>3490</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>129614</v>
+        <v>1191</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>150455</v>
+        <v>8450</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.6731985101694751</v>
+        <v>0.01676421487535934</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.6225179847811173</v>
+        <v>0.005720877708856155</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.7226106036615243</v>
+        <v>0.04058242394332646</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>455</v>
+        <v>10</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>297364</v>
+        <v>6949</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>281917</v>
+        <v>3160</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>314180</v>
+        <v>11909</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.6386073451069607</v>
+        <v>0.01492263602966899</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.6054333595595206</v>
+        <v>0.006785597074754612</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.6747192082092355</v>
+        <v>0.02557632622089983</v>
       </c>
     </row>
     <row r="11">
@@ -4646,213 +4646,213 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>4</v>
+        <v>64</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>2627</v>
+        <v>46127</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>649</v>
+        <v>36999</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>5900</v>
+        <v>56162</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.01406855649713637</v>
+        <v>0.2470304643560788</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.003473020511953218</v>
+        <v>0.1981481221731877</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.03159504946559633</v>
+        <v>0.3007746610993537</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>4</v>
+        <v>71</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>2302</v>
+        <v>49860</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>596</v>
+        <v>40129</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>5733</v>
+        <v>60242</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.01218496446787933</v>
+        <v>0.2639491651085389</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.003155456951304949</v>
+        <v>0.2124351335519379</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.03035130940793919</v>
+        <v>0.3189126918764946</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>8</v>
+        <v>135</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>4929</v>
+        <v>95987</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>2005</v>
+        <v>84278</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>9924</v>
+        <v>112148</v>
       </c>
       <c r="U12" s="6" t="n">
-        <v>0.01312131281873688</v>
+        <v>0.2555387464498514</v>
       </c>
       <c r="V12" s="6" t="n">
-        <v>0.005338974215631761</v>
+        <v>0.224366898547565</v>
       </c>
       <c r="W12" s="6" t="n">
-        <v>0.02642115282062363</v>
+        <v>0.29856160373028</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>64</v>
+        <v>192</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>46127</v>
+        <v>137972</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>36999</v>
+        <v>127485</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>56162</v>
+        <v>147395</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.2470304643560788</v>
+        <v>0.7389009791467848</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.1981481221731877</v>
+        <v>0.6827369481184351</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.3007746610993537</v>
+        <v>0.7893633338779005</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>71</v>
+        <v>197</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>49860</v>
+        <v>136738</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>40129</v>
+        <v>126158</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>60242</v>
+        <v>146687</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.2639491651085389</v>
+        <v>0.7238658704235817</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.2124351335519379</v>
+        <v>0.6678576227806794</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.3189126918764946</v>
+        <v>0.7765379827363587</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>135</v>
+        <v>389</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>95987</v>
+        <v>274710</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>84278</v>
+        <v>259034</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>112148</v>
+        <v>286793</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.2555387464498514</v>
+        <v>0.7313399407314117</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.224366898547565</v>
+        <v>0.6896055697809812</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.29856160373028</v>
+        <v>0.7635071860309953</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>192</v>
+        <v>4</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>137972</v>
+        <v>2627</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>127485</v>
+        <v>649</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>147395</v>
+        <v>5900</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.7389009791467848</v>
+        <v>0.01406855649713637</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.6827369481184351</v>
+        <v>0.003473020511953218</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.7893633338779005</v>
+        <v>0.03159504946559633</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>197</v>
+        <v>4</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>136738</v>
+        <v>2302</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>126158</v>
+        <v>596</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>146687</v>
+        <v>5733</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.7238658704235817</v>
+        <v>0.01218496446787933</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.6678576227806794</v>
+        <v>0.003155456951304949</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.7765379827363587</v>
+        <v>0.03035130940793919</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>389</v>
+        <v>8</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>274710</v>
+        <v>4929</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>259034</v>
+        <v>2005</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>286793</v>
+        <v>9924</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.7313399407314117</v>
+        <v>0.01312131281873688</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.6896055697809812</v>
+        <v>0.005338974215631761</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.7635071860309953</v>
+        <v>0.02642115282062363</v>
       </c>
     </row>
     <row r="15">
@@ -4934,213 +4934,213 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>1477</v>
+        <v>26291</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0</v>
+        <v>19412</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>5252</v>
+        <v>35010</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.008666878070131945</v>
+        <v>0.1542460804672511</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0</v>
+        <v>0.1138855566136418</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.03081305799235609</v>
+        <v>0.2053957985237456</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>524</v>
+        <v>31171</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>0</v>
+        <v>23404</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>2676</v>
+        <v>40029</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.003032031448611911</v>
+        <v>0.1804099489314709</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0</v>
+        <v>0.1354600537923895</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.01548797196472342</v>
+        <v>0.2316791438885553</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="R16" s="5" t="n">
-        <v>2001</v>
+        <v>57462</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>520</v>
+        <v>47112</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>5125</v>
+        <v>71632</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.005830351585274937</v>
+        <v>0.1674167150612154</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.001514873554482385</v>
+        <v>0.1372637068242854</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.01493123044764083</v>
+        <v>0.2087030818454503</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>35</v>
+        <v>193</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>26291</v>
+        <v>142681</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>19412</v>
+        <v>133932</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>35010</v>
+        <v>150123</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.1542460804672511</v>
+        <v>0.837087041462617</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.1138855566136418</v>
+        <v>0.7857623358420228</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.2053957985237456</v>
+        <v>0.8807489164758273</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>44</v>
+        <v>200</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>31171</v>
+        <v>141082</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>23404</v>
+        <v>131943</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>40029</v>
+        <v>148975</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.1804099489314709</v>
+        <v>0.8165580196199171</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.1354600537923895</v>
+        <v>0.7636606425545049</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.2316791438885553</v>
+        <v>0.8622363178568477</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>79</v>
+        <v>393</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>57462</v>
+        <v>283763</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>47112</v>
+        <v>270305</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>71632</v>
+        <v>294562</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.1674167150612154</v>
+        <v>0.8267529333535097</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.1372637068242854</v>
+        <v>0.7875430491799947</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.2087030818454503</v>
+        <v>0.8582150885447011</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>193</v>
+        <v>2</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>142681</v>
+        <v>1477</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>133932</v>
+        <v>0</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>150123</v>
+        <v>5252</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.837087041462617</v>
+        <v>0.008666878070131945</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.7857623358420228</v>
+        <v>0</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.8807489164758273</v>
+        <v>0.03081305799235609</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>141082</v>
+        <v>524</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>131943</v>
+        <v>0</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>148975</v>
+        <v>2676</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.8165580196199171</v>
+        <v>0.003032031448611911</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.7636606425545049</v>
+        <v>0</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.8622363178568477</v>
+        <v>0.01548797196472342</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>393</v>
+        <v>3</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>283763</v>
+        <v>2001</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>270305</v>
+        <v>520</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>294562</v>
+        <v>5125</v>
       </c>
       <c r="U18" s="6" t="n">
-        <v>0.8267529333535097</v>
+        <v>0.005830351585274937</v>
       </c>
       <c r="V18" s="6" t="n">
-        <v>0.7875430491799947</v>
+        <v>0.001514873554482385</v>
       </c>
       <c r="W18" s="6" t="n">
-        <v>0.8582150885447011</v>
+        <v>0.01493123044764083</v>
       </c>
     </row>
     <row r="19">
@@ -5222,213 +5222,213 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>18</v>
+        <v>335</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>11373</v>
+        <v>232593</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>6534</v>
+        <v>211213</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>17383</v>
+        <v>253967</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.01540533868527224</v>
+        <v>0.3150635773624768</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.008850896009006877</v>
+        <v>0.2861024106694964</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.02354584038101045</v>
+        <v>0.3440162031320989</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>20</v>
+        <v>316</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>12145</v>
+        <v>206513</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>7840</v>
+        <v>185452</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>18275</v>
+        <v>225030</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.01736918897859021</v>
+        <v>0.2953341816490889</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.0112119473229022</v>
+        <v>0.2652139349537481</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.02613524002767794</v>
+        <v>0.3218151736648645</v>
       </c>
       <c r="Q20" s="5" t="n">
-        <v>38</v>
+        <v>651</v>
       </c>
       <c r="R20" s="5" t="n">
-        <v>23518</v>
+        <v>439106</v>
       </c>
       <c r="S20" s="5" t="n">
-        <v>17054</v>
+        <v>413010</v>
       </c>
       <c r="T20" s="5" t="n">
-        <v>32294</v>
+        <v>468639</v>
       </c>
       <c r="U20" s="6" t="n">
-        <v>0.01636063138259591</v>
+        <v>0.3054664366273929</v>
       </c>
       <c r="V20" s="6" t="n">
-        <v>0.01186368418093788</v>
+        <v>0.2873125050273043</v>
       </c>
       <c r="W20" s="6" t="n">
-        <v>0.02246525665392955</v>
+        <v>0.326011047099263</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>335</v>
+        <v>702</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>232593</v>
+        <v>494276</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>211213</v>
+        <v>473777</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>253967</v>
+        <v>515717</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.3150635773624768</v>
+        <v>0.6695310839522509</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.2861024106694964</v>
+        <v>0.6417632730683875</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.3440162031320989</v>
+        <v>0.6985747199617873</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>316</v>
+        <v>716</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>206513</v>
+        <v>480594</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>185452</v>
+        <v>461458</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>225030</v>
+        <v>500683</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.2953341816490889</v>
+        <v>0.6872966293723209</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.2652139349537481</v>
+        <v>0.6599298932045679</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.3218151736648645</v>
+        <v>0.7160248723910149</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>651</v>
+        <v>1418</v>
       </c>
       <c r="R21" s="5" t="n">
-        <v>439106</v>
+        <v>974870</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>413010</v>
+        <v>945109</v>
       </c>
       <c r="T21" s="5" t="n">
-        <v>468639</v>
+        <v>1001563</v>
       </c>
       <c r="U21" s="6" t="n">
-        <v>0.3054664366273929</v>
+        <v>0.6781729319900112</v>
       </c>
       <c r="V21" s="6" t="n">
-        <v>0.2873125050273043</v>
+        <v>0.6574696323566337</v>
       </c>
       <c r="W21" s="6" t="n">
-        <v>0.326011047099263</v>
+        <v>0.6967418884415597</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n"/>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>702</v>
+        <v>18</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>494276</v>
+        <v>11373</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>473777</v>
+        <v>6534</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>515717</v>
+        <v>17383</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.6695310839522509</v>
+        <v>0.01540533868527224</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.6417632730683875</v>
+        <v>0.008850896009006877</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.6985747199617873</v>
+        <v>0.02354584038101045</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>716</v>
+        <v>20</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>480594</v>
+        <v>12145</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>461458</v>
+        <v>7840</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>500683</v>
+        <v>18275</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.6872966293723209</v>
+        <v>0.01736918897859021</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.6599298932045679</v>
+        <v>0.0112119473229022</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.7160248723910149</v>
+        <v>0.02613524002767794</v>
       </c>
       <c r="Q22" s="5" t="n">
-        <v>1418</v>
+        <v>38</v>
       </c>
       <c r="R22" s="5" t="n">
-        <v>974870</v>
+        <v>23518</v>
       </c>
       <c r="S22" s="5" t="n">
-        <v>945109</v>
+        <v>17054</v>
       </c>
       <c r="T22" s="5" t="n">
-        <v>1001563</v>
+        <v>32294</v>
       </c>
       <c r="U22" s="6" t="n">
-        <v>0.6781729319900112</v>
+        <v>0.01636063138259591</v>
       </c>
       <c r="V22" s="6" t="n">
-        <v>0.6574696323566337</v>
+        <v>0.01186368418093788</v>
       </c>
       <c r="W22" s="6" t="n">
-        <v>0.6967418884415597</v>
+        <v>0.02246525665392955</v>
       </c>
     </row>
     <row r="23">
@@ -5742,213 +5742,213 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>1918</v>
+        <v>33448</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>308</v>
+        <v>28933</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>7068</v>
+        <v>38136</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.03795266162037221</v>
+        <v>0.6618526076872008</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.006084704496595087</v>
+        <v>0.5725125470902697</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.1398525859950681</v>
+        <v>0.7546223817210931</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>740</v>
+        <v>39298</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>0</v>
+        <v>34465</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>2616</v>
+        <v>42907</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.01431156038420908</v>
+        <v>0.7596593426836921</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0</v>
+        <v>0.6662429502023327</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.05056640483914481</v>
+        <v>0.8294261800315559</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>5</v>
+        <v>157</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>2658</v>
+        <v>72746</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>983</v>
+        <v>66389</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>6579</v>
+        <v>78737</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.02599420723946877</v>
+        <v>0.7113265034637444</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0.009608865249267977</v>
+        <v>0.6491669801340505</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.06432904011024143</v>
+        <v>0.7699061476504215</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>33448</v>
+        <v>15171</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>28933</v>
+        <v>10891</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>38136</v>
+        <v>19816</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.6618526076872008</v>
+        <v>0.3001947306924272</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.5725125470902697</v>
+        <v>0.215514890741244</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.7546223817210931</v>
+        <v>0.3921083692982444</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>78</v>
+        <v>28</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>39298</v>
+        <v>11693</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>34465</v>
+        <v>8207</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>42907</v>
+        <v>16634</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.7596593426836921</v>
+        <v>0.2260290969320989</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.6662429502023327</v>
+        <v>0.1586384581364221</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.8294261800315559</v>
+        <v>0.3215535252902224</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>157</v>
+        <v>62</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>72746</v>
+        <v>26864</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>66389</v>
+        <v>21044</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>78737</v>
+        <v>33043</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.7113265034637444</v>
+        <v>0.2626792892967869</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.6491669801340505</v>
+        <v>0.205769943785012</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.7699061476504215</v>
+        <v>0.3231045275431148</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>15171</v>
+        <v>1918</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>10891</v>
+        <v>308</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>19816</v>
+        <v>7068</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.3001947306924272</v>
+        <v>0.03795266162037221</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.215514890741244</v>
+        <v>0.006084704496595087</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.3921083692982444</v>
+        <v>0.1398525859950681</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>11693</v>
+        <v>740</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>8207</v>
+        <v>0</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>16634</v>
+        <v>2616</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.2260290969320989</v>
+        <v>0.01431156038420908</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.1586384581364221</v>
+        <v>0</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.3215535252902224</v>
+        <v>0.05056640483914481</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>62</v>
+        <v>5</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>26864</v>
+        <v>2658</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>21044</v>
+        <v>983</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>33043</v>
+        <v>6579</v>
       </c>
       <c r="U6" s="6" t="n">
-        <v>0.2626792892967869</v>
+        <v>0.02599420723946877</v>
       </c>
       <c r="V6" s="6" t="n">
-        <v>0.205769943785012</v>
+        <v>0.009608865249267977</v>
       </c>
       <c r="W6" s="6" t="n">
-        <v>0.3231045275431148</v>
+        <v>0.06432904011024143</v>
       </c>
     </row>
     <row r="7">
@@ -6030,205 +6030,205 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="5" t="inlineStr"/>
-      <c r="F8" s="5" t="inlineStr"/>
+        <v>53529</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>44719</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>63957</v>
+      </c>
       <c r="G8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
+        <v>0.3398187947089922</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>0.2838928673540951</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>0.4060178238054519</v>
+      </c>
       <c r="J8" s="5" t="n">
-        <v>2</v>
+        <v>98</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>1727</v>
+        <v>49173</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>0</v>
+        <v>40803</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>6031</v>
+        <v>57379</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.01186516632109639</v>
+        <v>0.337917694995041</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0</v>
+        <v>0.2803981490724007</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.041444863190832</v>
+        <v>0.3943104289952655</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>2</v>
+        <v>201</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>1727</v>
+        <v>102702</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>0</v>
+        <v>90490</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>5887</v>
+        <v>116543</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.005697585241367644</v>
+        <v>0.3389058974617519</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0</v>
+        <v>0.2986099966792065</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.01942635553991101</v>
+        <v>0.384581475831459</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>103</v>
+        <v>173</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>53529</v>
+        <v>103993</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>44719</v>
+        <v>93565</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>63957</v>
+        <v>112803</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.3398187947089922</v>
+        <v>0.6601812052910078</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.2838928673540951</v>
+        <v>0.5939821761945485</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.4060178238054519</v>
+        <v>0.7161071326459051</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>98</v>
+        <v>158</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>49173</v>
+        <v>94618</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>40803</v>
+        <v>86142</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>57379</v>
+        <v>103014</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.337917694995041</v>
+        <v>0.6502171386838625</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.2803981490724007</v>
+        <v>0.591971121092413</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.3943104289952655</v>
+        <v>0.7079135254749126</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>201</v>
+        <v>331</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>102702</v>
+        <v>198611</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>90490</v>
+        <v>184813</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>116543</v>
+        <v>210747</v>
       </c>
       <c r="U9" s="6" t="n">
-        <v>0.3389058974617519</v>
+        <v>0.6553965172968804</v>
       </c>
       <c r="V9" s="6" t="n">
-        <v>0.2986099966792065</v>
+        <v>0.6098640714869307</v>
       </c>
       <c r="W9" s="6" t="n">
-        <v>0.384581475831459</v>
+        <v>0.6954464770673772</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>173</v>
+        <v>0</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>103993</v>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>93565</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>112803</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="inlineStr"/>
       <c r="G10" s="6" t="n">
-        <v>0.6601812052910078</v>
-      </c>
-      <c r="H10" s="6" t="n">
-        <v>0.5939821761945485</v>
-      </c>
-      <c r="I10" s="6" t="n">
-        <v>0.7161071326459051</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H10" s="6" t="inlineStr"/>
+      <c r="I10" s="6" t="inlineStr"/>
       <c r="J10" s="5" t="n">
-        <v>158</v>
+        <v>2</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>94618</v>
+        <v>1727</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>86142</v>
+        <v>0</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>103014</v>
+        <v>6031</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.6502171386838625</v>
+        <v>0.01186516632109639</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.591971121092413</v>
+        <v>0</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.7079135254749126</v>
+        <v>0.041444863190832</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>331</v>
+        <v>2</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>198611</v>
+        <v>1727</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>184813</v>
+        <v>0</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>210747</v>
+        <v>5887</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.6553965172968804</v>
+        <v>0.005697585241367644</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.6098640714869307</v>
+        <v>0</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.6954464770673772</v>
+        <v>0.01942635553991101</v>
       </c>
     </row>
     <row r="11">
@@ -6310,205 +6310,205 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
+        <v>58991</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>47451</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>70523</v>
+      </c>
       <c r="G12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="6" t="inlineStr"/>
-      <c r="I12" s="6" t="inlineStr"/>
+        <v>0.2971528567490487</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.2390213031443931</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.3552452597765163</v>
+      </c>
       <c r="J12" s="5" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>2687</v>
+        <v>37263</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>868</v>
+        <v>28986</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>7169</v>
+        <v>47657</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.01538208857121721</v>
+        <v>0.2133322258523281</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.004967173371529041</v>
+        <v>0.165947702365431</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.04104394019499605</v>
+        <v>0.2728372836414679</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>3</v>
+        <v>126</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>2687</v>
+        <v>96254</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>868</v>
+        <v>82016</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>7570</v>
+        <v>112515</v>
       </c>
       <c r="U12" s="6" t="n">
-        <v>0.007199570219738973</v>
+        <v>0.2579206994766629</v>
       </c>
       <c r="V12" s="6" t="n">
-        <v>0.00232499404665399</v>
+        <v>0.2197680836382482</v>
       </c>
       <c r="W12" s="6" t="n">
-        <v>0.02028517765150954</v>
+        <v>0.3014942690947606</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>75</v>
+        <v>167</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>58991</v>
+        <v>139529</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>47451</v>
+        <v>127997</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>70523</v>
+        <v>151069</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.2971528567490487</v>
+        <v>0.7028471432509514</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.2390213031443931</v>
+        <v>0.6447547402234836</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.3552452597765163</v>
+        <v>0.7609786968556068</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>51</v>
+        <v>179</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>37263</v>
+        <v>134722</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>28986</v>
+        <v>123469</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>47657</v>
+        <v>143301</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.2133322258523281</v>
+        <v>0.7712856855764548</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.165947702365431</v>
+        <v>0.7068647557126205</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.2728372836414679</v>
+        <v>0.8203998608707758</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>126</v>
+        <v>346</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>96254</v>
+        <v>274251</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>82016</v>
+        <v>258199</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>112515</v>
+        <v>288234</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.2579206994766629</v>
+        <v>0.734879730303598</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.2197680836382482</v>
+        <v>0.691866779837488</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.3014942690947606</v>
+        <v>0.7723478728221223</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>139529</v>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>127997</v>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>151069</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="inlineStr"/>
       <c r="G14" s="6" t="n">
-        <v>0.7028471432509514</v>
-      </c>
-      <c r="H14" s="6" t="n">
-        <v>0.6447547402234836</v>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>0.7609786968556068</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H14" s="6" t="inlineStr"/>
+      <c r="I14" s="6" t="inlineStr"/>
       <c r="J14" s="5" t="n">
-        <v>179</v>
+        <v>3</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>134722</v>
+        <v>2687</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>123469</v>
+        <v>868</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>143301</v>
+        <v>7169</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.7712856855764548</v>
+        <v>0.01538208857121721</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.7068647557126205</v>
+        <v>0.004967173371529041</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.8203998608707758</v>
+        <v>0.04104394019499605</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>346</v>
+        <v>3</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>274251</v>
+        <v>2687</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>258199</v>
+        <v>868</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>288234</v>
+        <v>7570</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.734879730303598</v>
+        <v>0.007199570219738973</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.691866779837488</v>
+        <v>0.00232499404665399</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.7723478728221223</v>
+        <v>0.02028517765150954</v>
       </c>
     </row>
     <row r="15">
@@ -6590,213 +6590,213 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>5</v>
+        <v>58</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>5574</v>
+        <v>49434</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>1804</v>
+        <v>37260</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>13624</v>
+        <v>64501</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.01906608266005435</v>
+        <v>0.1690932047604673</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.006169343599831726</v>
+        <v>0.1274519729983213</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.04660124682787997</v>
+        <v>0.2206314144520866</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>4009</v>
+        <v>45762</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>1250</v>
+        <v>36402</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>8858</v>
+        <v>57193</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.01594366022453574</v>
+        <v>0.1819764620702499</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.00496888829753926</v>
+        <v>0.1447555940808207</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.03522657200846403</v>
+        <v>0.2274317592030971</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>10</v>
+        <v>123</v>
       </c>
       <c r="R16" s="5" t="n">
-        <v>9583</v>
+        <v>95196</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>4728</v>
+        <v>78545</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>18482</v>
+        <v>112428</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.01762221492438086</v>
+        <v>0.1750506688589742</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.008693820249074467</v>
+        <v>0.1444327749311647</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.03398650793923758</v>
+        <v>0.2067387500849019</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>58</v>
+        <v>278</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>49434</v>
+        <v>237338</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>37260</v>
+        <v>220907</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>64501</v>
+        <v>249512</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.1690932047604673</v>
+        <v>0.8118407125794782</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.1274519729983213</v>
+        <v>0.7556347469501424</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.2206314144520866</v>
+        <v>0.8534827251536357</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>65</v>
+        <v>265</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>45762</v>
+        <v>201701</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>36402</v>
+        <v>189759</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>57193</v>
+        <v>211535</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.1819764620702499</v>
+        <v>0.8020798777052145</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.1447555940808207</v>
+        <v>0.7545912756594496</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.2274317592030971</v>
+        <v>0.8411856082749638</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>123</v>
+        <v>543</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>95196</v>
+        <v>439039</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>78545</v>
+        <v>420685</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>112428</v>
+        <v>457466</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.1750506688589742</v>
+        <v>0.8073271162166449</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.1444327749311647</v>
+        <v>0.773577445230188</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.2067387500849019</v>
+        <v>0.8412119037172283</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>278</v>
+        <v>5</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>237338</v>
+        <v>5574</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>220907</v>
+        <v>1804</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>249512</v>
+        <v>13624</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.8118407125794782</v>
+        <v>0.01906608266005435</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.7556347469501424</v>
+        <v>0.006169343599831726</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.8534827251536357</v>
+        <v>0.04660124682787997</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>265</v>
+        <v>5</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>201701</v>
+        <v>4009</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>189759</v>
+        <v>1250</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>211535</v>
+        <v>8858</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.8020798777052145</v>
+        <v>0.01594366022453574</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.7545912756594496</v>
+        <v>0.00496888829753926</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.8411856082749638</v>
+        <v>0.03522657200846403</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>543</v>
+        <v>10</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>439039</v>
+        <v>9583</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>420685</v>
+        <v>4728</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>457466</v>
+        <v>18482</v>
       </c>
       <c r="U18" s="6" t="n">
-        <v>0.8073271162166449</v>
+        <v>0.01762221492438086</v>
       </c>
       <c r="V18" s="6" t="n">
-        <v>0.773577445230188</v>
+        <v>0.008693820249074467</v>
       </c>
       <c r="W18" s="6" t="n">
-        <v>0.8412119037172283</v>
+        <v>0.03398650793923758</v>
       </c>
     </row>
     <row r="19">
@@ -6878,213 +6878,213 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>8</v>
+        <v>315</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>7492</v>
+        <v>195402</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>3359</v>
+        <v>173560</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>16163</v>
+        <v>217575</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.01071921357550712</v>
+        <v>0.2795744929608477</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.004805967813107631</v>
+        <v>0.2483245280293698</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.02312589527033307</v>
+        <v>0.3112999254701128</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>12</v>
+        <v>292</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>9163</v>
+        <v>171496</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>4792</v>
+        <v>154387</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>16437</v>
+        <v>189792</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.01469883667186344</v>
+        <v>0.2751008726237343</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.007686591910131019</v>
+        <v>0.2476567729280766</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.02636742748933856</v>
+        <v>0.3044497344707969</v>
       </c>
       <c r="Q20" s="5" t="n">
-        <v>20</v>
+        <v>607</v>
       </c>
       <c r="R20" s="5" t="n">
-        <v>16655</v>
+        <v>366897</v>
       </c>
       <c r="S20" s="5" t="n">
-        <v>10375</v>
+        <v>339486</v>
       </c>
       <c r="T20" s="5" t="n">
-        <v>27016</v>
+        <v>399201</v>
       </c>
       <c r="U20" s="6" t="n">
-        <v>0.01259536398536086</v>
+        <v>0.2774654528769538</v>
       </c>
       <c r="V20" s="6" t="n">
-        <v>0.007845832296568182</v>
+        <v>0.2567355397286693</v>
       </c>
       <c r="W20" s="6" t="n">
-        <v>0.02043085630890165</v>
+        <v>0.3018949639309458</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>315</v>
+        <v>652</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>195402</v>
+        <v>496031</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>173560</v>
+        <v>473783</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>217575</v>
+        <v>518880</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.2795744929608477</v>
+        <v>0.7097062934636452</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.2483245280293698</v>
+        <v>0.6778740019407858</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.3112999254701128</v>
+        <v>0.7423967959422112</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>292</v>
+        <v>630</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>171496</v>
+        <v>442733</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>154387</v>
+        <v>424474</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>189792</v>
+        <v>460390</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.2751008726237343</v>
+        <v>0.7102002907044023</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.2476567729280766</v>
+        <v>0.6809106637646439</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.3044497344707969</v>
+        <v>0.7385235010908741</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>607</v>
+        <v>1282</v>
       </c>
       <c r="R21" s="5" t="n">
-        <v>366897</v>
+        <v>938765</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>339486</v>
+        <v>904712</v>
       </c>
       <c r="T21" s="5" t="n">
-        <v>399201</v>
+        <v>966284</v>
       </c>
       <c r="U21" s="6" t="n">
-        <v>0.2774654528769538</v>
+        <v>0.7099391831376854</v>
       </c>
       <c r="V21" s="6" t="n">
-        <v>0.2567355397286693</v>
+        <v>0.6841866096325415</v>
       </c>
       <c r="W21" s="6" t="n">
-        <v>0.3018949639309458</v>
+        <v>0.7307505790130875</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n"/>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>652</v>
+        <v>8</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>496031</v>
+        <v>7492</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>473783</v>
+        <v>3359</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>518880</v>
+        <v>16163</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.7097062934636452</v>
+        <v>0.01071921357550712</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.6778740019407858</v>
+        <v>0.004805967813107631</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.7423967959422112</v>
+        <v>0.02312589527033307</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>630</v>
+        <v>12</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>442733</v>
+        <v>9163</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>424474</v>
+        <v>4792</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>460390</v>
+        <v>16437</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.7102002907044023</v>
+        <v>0.01469883667186344</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.6809106637646439</v>
+        <v>0.007686591910131019</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.7385235010908741</v>
+        <v>0.02636742748933856</v>
       </c>
       <c r="Q22" s="5" t="n">
-        <v>1282</v>
+        <v>20</v>
       </c>
       <c r="R22" s="5" t="n">
-        <v>938765</v>
+        <v>16655</v>
       </c>
       <c r="S22" s="5" t="n">
-        <v>904712</v>
+        <v>10375</v>
       </c>
       <c r="T22" s="5" t="n">
-        <v>966284</v>
+        <v>27016</v>
       </c>
       <c r="U22" s="6" t="n">
-        <v>0.7099391831376854</v>
+        <v>0.01259536398536086</v>
       </c>
       <c r="V22" s="6" t="n">
-        <v>0.6841866096325415</v>
+        <v>0.007845832296568182</v>
       </c>
       <c r="W22" s="6" t="n">
-        <v>0.7307505790130875</v>
+        <v>0.02043085630890165</v>
       </c>
     </row>
     <row r="23">
